--- a/Ferias-template.xlsx
+++ b/Ferias-template.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ferias" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,14 +15,16 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ferias'!$A$1:$G$16</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,7 +35,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -42,7 +43,13 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
@@ -55,7 +62,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -64,22 +71,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002D3748"/>
+        <fgColor rgb="FF2D3748"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6F6D5"/>
+        <fgColor rgb="FFC6F6D5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDF2F7"/>
+        <fgColor rgb="FFEDF2F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEFCBF"/>
+        <fgColor rgb="FFFEFCBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF305496"/>
       </patternFill>
     </fill>
     <fill>
@@ -98,23 +110,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="FFE2E8F0"/>
       </left>
       <right style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="FFE2E8F0"/>
       </right>
       <top style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="FFE2E8F0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E2E8F0"/>
+        <color rgb="FFE2E8F0"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -134,15 +147,18 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -227,11 +243,13 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblIntegrantes" displayName="tblIntegrantes" ref="A1:B14" headerRowCount="1">
-  <autoFilter ref="A1:B14"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblIntegrantes" displayName="tblIntegrantes" ref="A1:D14" headerRowCount="1">
+  <autoFilter ref="A1:D14"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="Integrante"/>
     <tableColumn id="2" name="Squad"/>
+    <tableColumn id="3" name="Data de inicio na AIR"/>
+    <tableColumn id="4" name="Data das ultimas ferias"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -542,8 +560,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1209,11 +1226,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1227,6 +1246,16 @@
           <t>Squad</t>
         </is>
       </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Data de inicio na AIR</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Data das ultimas ferias</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1239,6 +1268,10 @@
           <t>Cross</t>
         </is>
       </c>
+      <c r="C2" s="10" t="n">
+        <v>45366</v>
+      </c>
+      <c r="D2" s="10" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1251,6 +1284,10 @@
           <t>Mobile</t>
         </is>
       </c>
+      <c r="C3" s="10" t="n">
+        <v>45463</v>
+      </c>
+      <c r="D3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1263,6 +1300,10 @@
           <t>Pedido/OMS - Integração</t>
         </is>
       </c>
+      <c r="C4" s="10" t="n">
+        <v>45547</v>
+      </c>
+      <c r="D4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1275,6 +1316,10 @@
           <t>Frontend &amp; CMS</t>
         </is>
       </c>
+      <c r="C5" s="10" t="n">
+        <v>45872</v>
+      </c>
+      <c r="D5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1287,6 +1332,12 @@
           <t>Jornada de Compras</t>
         </is>
       </c>
+      <c r="C6" s="10" t="n">
+        <v>45390</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>45731</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1299,6 +1350,10 @@
           <t>Cross</t>
         </is>
       </c>
+      <c r="C7" s="10" t="n">
+        <v>46032</v>
+      </c>
+      <c r="D7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1311,6 +1366,12 @@
           <t>Pedido/OMS</t>
         </is>
       </c>
+      <c r="C8" s="10" t="n">
+        <v>45461</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>46078</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1323,6 +1384,10 @@
           <t>Frontend &amp; CMS</t>
         </is>
       </c>
+      <c r="C9" s="10" t="n">
+        <v>46075</v>
+      </c>
+      <c r="D9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1335,6 +1400,8 @@
           <t>Mobile</t>
         </is>
       </c>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1347,6 +1414,12 @@
           <t>Mobile</t>
         </is>
       </c>
+      <c r="C11" s="10" t="n">
+        <v>45424</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>46111</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1359,6 +1432,10 @@
           <t>Frontend &amp; CMS</t>
         </is>
       </c>
+      <c r="C12" s="10" t="n">
+        <v>46036</v>
+      </c>
+      <c r="D12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1371,6 +1448,10 @@
           <t>Frontend/Backoffice</t>
         </is>
       </c>
+      <c r="C13" s="10" t="n">
+        <v>45332</v>
+      </c>
+      <c r="D13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1383,6 +1464,8 @@
           <t>Frontend &amp; CMS</t>
         </is>
       </c>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1446,22 +1529,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Instrucoes de uso</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1493,7 +1574,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - Integrantes: lista de pessoas (use a aba 'Integrantes', com nome + squad).</t>
+          <t xml:space="preserve">     - Integrantes: cadastro mestre de pessoas (nome, squad, admissao, ultimas ferias).</t>
         </is>
       </c>
     </row>
@@ -1507,50 +1588,111 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4. Pra adicionar um squad/integrante novo, ir na aba correspondente e colar/digitar</t>
+          <t>3a. Aba 'Integrantes' tem 4 colunas:</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   no fim da tabela. O dropdown puxa automaticamente.</t>
+          <t xml:space="preserve">     - Integrante:               nome do colaborador</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5. Mes: use Janeiro, Fevereiro, Março, Abril, Maio, Junho, Julho, Agosto, Setembro,</t>
+          <t xml:space="preserve">     - Squad:                    squad atual</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Outubro, Novembro, Dezembro.</t>
+          <t xml:space="preserve">     - Data de inicio na AIR:    data de admissao na empresa (dd/mm/aaaa)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6. Inicio/Fim: formato dd/mm/aaaa (ex: 12/01/2026).</t>
+          <t xml:space="preserve">     - Data das ultimas ferias:  data fim do ultimo periodo de ferias tirado</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7. Dias: numero inteiro.</t>
+          <t xml:space="preserve">                                 (vazio se a pessoa nunca tirou ferias)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Essas datas alimentam a secao 'Controle de Vencimento de Ferias' no</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    relatorio gerado, com 1o e 2o vencimento por colaborador (CLT 12/24 meses).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Atualize a 'Data das ultimas ferias' manualmente quando alguem voltar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4. Pra adicionar um squad/integrante novo, ir na aba correspondente e colar/digitar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   no fim da tabela. O dropdown puxa automaticamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5. Mes: use Janeiro, Fevereiro, Março, Abril, Maio, Junho, Julho, Agosto, Setembro,</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Outubro, Novembro, Dezembro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6. Inicio/Fim: formato dd/mm/aaaa (ex: 12/01/2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>7. Dias: numero inteiro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Apos editar, salve o arquivo e gere o relatorio pelo atalho "Gerar Relatorio".</t>
         </is>
